--- a/InputData/elec/SoTaDCCbIC/Share of Transmission and Distribution Capital Costs by ISIC Code.xlsx
+++ b/InputData/elec/SoTaDCCbIC/Share of Transmission and Distribution Capital Costs by ISIC Code.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27528"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -18,7 +18,7 @@
     <sheet name="Cost Breakdowns" sheetId="1" r:id="rId3"/>
     <sheet name="SoTaDCCbIC" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,448 +41,448 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="148">
   <si>
+    <t>SoTCCbIC Share of Transmission and Distribution Capital Costs by ISIC Code</t>
+  </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>NREL</t>
+  </si>
+  <si>
+    <t>JEDI Transmission Model</t>
+  </si>
+  <si>
+    <t>https://www.nrel.gov/analysis/jedi/transmission-line.html</t>
+  </si>
+  <si>
+    <t>"DefaultData" and "Calculations" tabs</t>
+  </si>
+  <si>
+    <t>OECD Code</t>
+  </si>
+  <si>
+    <t>ISIC Code</t>
+  </si>
+  <si>
+    <t>D01T03: Agriculture, forestry and fishing</t>
+  </si>
+  <si>
+    <t>ISIC 01T03</t>
+  </si>
+  <si>
+    <t>D05: Coal mining</t>
+  </si>
+  <si>
+    <t>ISIC 05</t>
+  </si>
+  <si>
+    <t>D06: Oil and gas extraction</t>
+  </si>
+  <si>
+    <t>ISIC 06</t>
+  </si>
+  <si>
+    <t>D07T08: Mining and quarrying of uranium and non-energy-producing products</t>
+  </si>
+  <si>
+    <t>ISIC 07T08</t>
+  </si>
+  <si>
+    <t>D09: Mining support service activities</t>
+  </si>
+  <si>
+    <t>ISIC 09</t>
+  </si>
+  <si>
+    <t>D10T12: Food products, beverages and tobacco</t>
+  </si>
+  <si>
+    <t>ISIC 10T12</t>
+  </si>
+  <si>
+    <t>D13T15: Textiles, wearing apparel, leather and related products</t>
+  </si>
+  <si>
+    <t>ISIC 13T15</t>
+  </si>
+  <si>
+    <t>D16: Wood and products of wood and cork</t>
+  </si>
+  <si>
+    <t>ISIC 16</t>
+  </si>
+  <si>
+    <t>D17T18: Paper products and printing</t>
+  </si>
+  <si>
+    <t>ISIC 17T18</t>
+  </si>
+  <si>
+    <t>D19: Coke and refined petroleum products</t>
+  </si>
+  <si>
+    <t>ISIC 19</t>
+  </si>
+  <si>
+    <t>D20: Chemicals</t>
+  </si>
+  <si>
+    <t>ISIC 20</t>
+  </si>
+  <si>
+    <t>D21: Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>ISIC 21</t>
+  </si>
+  <si>
+    <t>D22: Rubber and plastic products</t>
+  </si>
+  <si>
+    <t>ISIC 22</t>
+  </si>
+  <si>
+    <t>D231: Glass</t>
+  </si>
+  <si>
+    <t>ISIC 231</t>
+  </si>
+  <si>
+    <t>D239: Cement and other nometallic minerals</t>
+  </si>
+  <si>
+    <t>ISIC 239</t>
+  </si>
+  <si>
+    <t>D241: Iron and steel</t>
+  </si>
+  <si>
+    <t>ISIC 241</t>
+  </si>
+  <si>
+    <t>D242: Other metals</t>
+  </si>
+  <si>
+    <t>ISIC 242</t>
+  </si>
+  <si>
+    <t>D25: Fabricated metal products</t>
+  </si>
+  <si>
+    <t>ISIC 25</t>
+  </si>
+  <si>
+    <t>D26: Computer, electronic and optical products</t>
+  </si>
+  <si>
+    <t>ISIC 26</t>
+  </si>
+  <si>
+    <t>D27: Electrical equipment</t>
+  </si>
+  <si>
+    <t>ISIC 27</t>
+  </si>
+  <si>
+    <t>D28: Machinery and equipment, nec</t>
+  </si>
+  <si>
+    <t>ISIC 28</t>
+  </si>
+  <si>
+    <t>D29: Motor vehicles, trailers and semi-trailers</t>
+  </si>
+  <si>
+    <t>ISIC 29</t>
+  </si>
+  <si>
+    <t>D30: Other transport equipment</t>
+  </si>
+  <si>
+    <t>ISIC 30</t>
+  </si>
+  <si>
+    <t>D31T33: Other manufacturing; repair and installation of machinery and equipment</t>
+  </si>
+  <si>
+    <t>ISIC 31T33</t>
+  </si>
+  <si>
+    <t>D351: Electricity generation and distribution</t>
+  </si>
+  <si>
+    <t>ISIC 351</t>
+  </si>
+  <si>
+    <t>D352T353: Energy pipelines and gas processing</t>
+  </si>
+  <si>
+    <t>ISIC 352T353</t>
+  </si>
+  <si>
+    <t>D36T39: Water and waste</t>
+  </si>
+  <si>
+    <t>ISIC 36T39</t>
+  </si>
+  <si>
+    <t>D41T43: Construction</t>
+  </si>
+  <si>
+    <t>ISIC 41T43</t>
+  </si>
+  <si>
+    <t>D45T47: Wholesale and retail trade; repair of motor vehicles</t>
+  </si>
+  <si>
+    <t>ISIC 45T47</t>
+  </si>
+  <si>
+    <t>D49T53: Transportation and storage</t>
+  </si>
+  <si>
+    <t>ISIC 49T53</t>
+  </si>
+  <si>
+    <t>D55T56: Accomodation and food services</t>
+  </si>
+  <si>
+    <t>ISIC 55T56</t>
+  </si>
+  <si>
+    <t>D58T60: Publishing, audiovisual and broadcasting activities</t>
+  </si>
+  <si>
+    <t>ISIC 58T60</t>
+  </si>
+  <si>
+    <t>D61: Telecommunications</t>
+  </si>
+  <si>
+    <t>ISIC 61</t>
+  </si>
+  <si>
+    <t>D62T63: IT and other information services</t>
+  </si>
+  <si>
+    <t>ISIC 62T63</t>
+  </si>
+  <si>
+    <t>D64T66: Financial and insurance activities</t>
+  </si>
+  <si>
+    <t>ISIC 64T66</t>
+  </si>
+  <si>
+    <t>D68: Real estate activities</t>
+  </si>
+  <si>
+    <t>ISIC 68</t>
+  </si>
+  <si>
+    <t>D69T82: Other business sector services</t>
+  </si>
+  <si>
+    <t>ISIC 69T82</t>
+  </si>
+  <si>
+    <t>D84: Public admin. and defence; compulsory social security</t>
+  </si>
+  <si>
+    <t>ISIC 84</t>
+  </si>
+  <si>
+    <t>D85: Education</t>
+  </si>
+  <si>
+    <t>ISIC 85</t>
+  </si>
+  <si>
+    <t>D86T88: Human health and social work</t>
+  </si>
+  <si>
+    <t>ISIC 86T88</t>
+  </si>
+  <si>
+    <t>D90T96: Arts, entertainment, recreation and other service activities</t>
+  </si>
+  <si>
+    <t>ISIC 90T96</t>
+  </si>
+  <si>
+    <t>D97T98: Private households with employed persons</t>
+  </si>
+  <si>
+    <t>ISIC 97T98</t>
+  </si>
+  <si>
+    <t>Transmission</t>
+  </si>
+  <si>
     <t>Capital Costs</t>
   </si>
   <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Percent of Cost</t>
+  </si>
+  <si>
+    <t>OECD Mapping</t>
+  </si>
+  <si>
+    <t>ISIC Mapping</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">  Development and Preconstruction Activites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Land Acquisition Services</t>
+  </si>
+  <si>
+    <t>Mapping based on I-JEDI and judgment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Private Land Acquisition Payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Engineering/Surveying/Geotechnical Consulting Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Environmental &amp; Permitting Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subtotal Development and Preconstruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Construction Activities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Materials &amp; Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Concrete, gravel, asphalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Steel structures and poles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Overhead wires (conductor and insulators and shield wire)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subtotal Materials &amp; Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Labor/Installation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Civil (grading, roads, site prep, foundations, fencing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Heavy Construction (Tower erection, Conductor stringing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subtotal Labor/Installation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Total Transmission Line Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Infrastructure Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Positions (new bays/circuits)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    New Substation Facilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Existing Substation Facilities (upgrades)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Transformers, Series Compensation, etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Converter Station (includes ground electrode)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    New Substation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Converter Station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subtotal Labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Total Infrastructure Costs</t>
+  </si>
+  <si>
+    <t>Services/Other Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Transmission Line Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  T-Line Management Services (Site mgmt, legal, lands, ins, PR, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  T-Line Engineering, Const Mgmt, &amp; Environmental Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Infrastructure Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Substation Management Services (Site mgmt, legal, lands, PR, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Substation Engineering, Const Mgmt, &amp; Environmental Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Other Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Environmental Mitigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  System Operator and Regulator Fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Miscellanous Business Services and Utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Construction Insurance (Substation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Subtotal Other Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Total Services/Other Costs</t>
+  </si>
+  <si>
     <t>Subtotal All Costs (without sales tax)</t>
   </si>
   <si>
     <t>Sales Tax (Materials &amp; Equipment Purchases)</t>
   </si>
   <si>
-    <t xml:space="preserve"> Subtotal</t>
-  </si>
-  <si>
-    <t>D01T03: Agriculture, forestry and fishing</t>
-  </si>
-  <si>
-    <t>D09: Mining support service activities</t>
-  </si>
-  <si>
-    <t>D10T12: Food products, beverages and tobacco</t>
-  </si>
-  <si>
-    <t>D13T15: Textiles, wearing apparel, leather and related products</t>
-  </si>
-  <si>
-    <t>D16: Wood and products of wood and cork</t>
-  </si>
-  <si>
-    <t>D17T18: Paper products and printing</t>
-  </si>
-  <si>
-    <t>D19: Coke and refined petroleum products</t>
-  </si>
-  <si>
-    <t>D22: Rubber and plastic products</t>
-  </si>
-  <si>
-    <t>D25: Fabricated metal products</t>
-  </si>
-  <si>
-    <t>D26: Computer, electronic and optical products</t>
-  </si>
-  <si>
-    <t>D27: Electrical equipment</t>
-  </si>
-  <si>
-    <t>D28: Machinery and equipment, nec</t>
-  </si>
-  <si>
-    <t>D29: Motor vehicles, trailers and semi-trailers</t>
-  </si>
-  <si>
-    <t>D30: Other transport equipment</t>
-  </si>
-  <si>
-    <t>D31T33: Other manufacturing; repair and installation of machinery and equipment</t>
-  </si>
-  <si>
-    <t>D41T43: Construction</t>
-  </si>
-  <si>
-    <t>D45T47: Wholesale and retail trade; repair of motor vehicles</t>
-  </si>
-  <si>
-    <t>D49T53: Transportation and storage</t>
-  </si>
-  <si>
-    <t>D55T56: Accomodation and food services</t>
-  </si>
-  <si>
-    <t>D58T60: Publishing, audiovisual and broadcasting activities</t>
-  </si>
-  <si>
-    <t>D61: Telecommunications</t>
-  </si>
-  <si>
-    <t>D62T63: IT and other information services</t>
-  </si>
-  <si>
-    <t>D64T66: Financial and insurance activities</t>
-  </si>
-  <si>
-    <t>D68: Real estate activities</t>
-  </si>
-  <si>
-    <t>D69T82: Other business sector services</t>
-  </si>
-  <si>
-    <t>D84: Public admin. and defence; compulsory social security</t>
-  </si>
-  <si>
-    <t>D85: Education</t>
-  </si>
-  <si>
-    <t>D86T88: Human health and social work</t>
-  </si>
-  <si>
-    <t>D90T96: Arts, entertainment, recreation and other service activities</t>
-  </si>
-  <si>
-    <t>D97T98: Private households with employed persons</t>
-  </si>
-  <si>
-    <t>ISIC 01T03</t>
-  </si>
-  <si>
-    <t>ISIC 07T08</t>
-  </si>
-  <si>
-    <t>ISIC 09</t>
-  </si>
-  <si>
-    <t>ISIC 10T12</t>
-  </si>
-  <si>
-    <t>ISIC 13T15</t>
-  </si>
-  <si>
-    <t>ISIC 16</t>
-  </si>
-  <si>
-    <t>ISIC 17T18</t>
-  </si>
-  <si>
-    <t>ISIC 19</t>
-  </si>
-  <si>
-    <t>ISIC 22</t>
-  </si>
-  <si>
-    <t>ISIC 25</t>
-  </si>
-  <si>
-    <t>ISIC 26</t>
-  </si>
-  <si>
-    <t>ISIC 27</t>
-  </si>
-  <si>
-    <t>ISIC 28</t>
-  </si>
-  <si>
-    <t>ISIC 29</t>
-  </si>
-  <si>
-    <t>ISIC 30</t>
-  </si>
-  <si>
-    <t>ISIC 31T33</t>
-  </si>
-  <si>
-    <t>ISIC 41T43</t>
-  </si>
-  <si>
-    <t>ISIC 45T47</t>
-  </si>
-  <si>
-    <t>ISIC 49T53</t>
-  </si>
-  <si>
-    <t>ISIC 55T56</t>
-  </si>
-  <si>
-    <t>ISIC 58T60</t>
-  </si>
-  <si>
-    <t>ISIC 61</t>
-  </si>
-  <si>
-    <t>ISIC 62T63</t>
-  </si>
-  <si>
-    <t>ISIC 64T66</t>
-  </si>
-  <si>
-    <t>ISIC 68</t>
-  </si>
-  <si>
-    <t>ISIC 69T82</t>
-  </si>
-  <si>
-    <t>ISIC 84</t>
-  </si>
-  <si>
-    <t>ISIC 85</t>
-  </si>
-  <si>
-    <t>ISIC 86T88</t>
-  </si>
-  <si>
-    <t>ISIC 90T96</t>
-  </si>
-  <si>
-    <t>ISIC 97T98</t>
-  </si>
-  <si>
-    <t>OECD Code</t>
-  </si>
-  <si>
-    <t>ISIC Code</t>
-  </si>
-  <si>
-    <t>ISIC Mapping</t>
-  </si>
-  <si>
-    <t>OECD Mapping</t>
-  </si>
-  <si>
-    <t>Mapping based on I-JEDI and judgment</t>
-  </si>
-  <si>
-    <t>NREL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Labor</t>
-  </si>
-  <si>
-    <t>"DefaultData" and "Calculations" tabs</t>
-  </si>
-  <si>
-    <t>ISIC 20</t>
-  </si>
-  <si>
-    <t>ISIC 21</t>
-  </si>
-  <si>
-    <t>D21: Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>D20: Chemicals</t>
-  </si>
-  <si>
-    <t>Transmission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Development and Preconstruction Activites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Land Acquisition Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Private Land Acquisition Payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Engineering/Surveying/Geotechnical Consulting Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Environmental &amp; Permitting Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Subtotal Development and Preconstruction</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Construction Activities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Materials &amp; Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Concrete, gravel, asphalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Steel structures and poles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Overhead wires (conductor and insulators and shield wire)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Subtotal Materials &amp; Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Labor/Installation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Civil (grading, roads, site prep, foundations, fencing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Heavy Construction (Tower erection, Conductor stringing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Subtotal Labor/Installation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Total Transmission Line Cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Infrastructure Costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Positions (new bays/circuits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    New Substation Facilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Existing Substation Facilities (upgrades)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Transformers, Series Compensation, etc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Converter Station (includes ground electrode)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    New Substation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Converter Station</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Subtotal Labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Total Infrastructure Costs</t>
-  </si>
-  <si>
-    <t>Services/Other Costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Transmission Line Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  T-Line Management Services (Site mgmt, legal, lands, ins, PR, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  T-Line Engineering, Const Mgmt, &amp; Environmental Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Infrastructure Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Substation Management Services (Site mgmt, legal, lands, PR, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Substation Engineering, Const Mgmt, &amp; Environmental Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Other Costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Environmental Mitigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  System Operator and Regulator Fees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Miscellanous Business Services and Utilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Construction Insurance (Substation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Subtotal Other Costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Total Services/Other Costs</t>
-  </si>
-  <si>
     <t>Total Project Cost</t>
   </si>
   <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Percent of Cost</t>
-  </si>
-  <si>
-    <t>https://www.nrel.gov/analysis/jedi/transmission-line.html</t>
+    <t>Unit: dimensionless (% of costs)</t>
   </si>
   <si>
     <t>transmission costs</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>JEDI Transmission Model</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (% of costs)</t>
-  </si>
-  <si>
-    <t>D06: Oil and gas extraction</t>
-  </si>
-  <si>
-    <t>D05: Coal mining</t>
-  </si>
-  <si>
-    <t>ISIC 05</t>
-  </si>
-  <si>
-    <t>ISIC 06</t>
-  </si>
-  <si>
-    <t>D07T08: Mining and quarrying of uranium and non-energy-producing products</t>
-  </si>
-  <si>
-    <t>D231: Glass</t>
-  </si>
-  <si>
-    <t>ISIC 231</t>
-  </si>
-  <si>
-    <t>D239: Cement and other nometallic minerals</t>
-  </si>
-  <si>
-    <t>ISIC 239</t>
-  </si>
-  <si>
-    <t>D241: Iron and steel</t>
-  </si>
-  <si>
-    <t>ISIC 241</t>
-  </si>
-  <si>
-    <t>D242: Other metals</t>
-  </si>
-  <si>
-    <t>ISIC 242</t>
-  </si>
-  <si>
-    <t>D351: Electricity generation and distribution</t>
-  </si>
-  <si>
-    <t>ISIC 351</t>
-  </si>
-  <si>
-    <t>D352T353: Energy pipelines and gas processing</t>
-  </si>
-  <si>
-    <t>ISIC 352T353</t>
-  </si>
-  <si>
-    <t>D36T39: Water and waste</t>
-  </si>
-  <si>
-    <t>ISIC 36T39</t>
-  </si>
-  <si>
-    <t>SoTCCbIC Share of Transmission and Distribution Capital Costs by ISIC Code</t>
   </si>
 </sst>
 </file>
@@ -495,7 +495,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1152,42 +1152,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="61.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="6" t="s">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="11">
         <v>2016</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="B6" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1201,7 +1201,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="77.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
@@ -1215,348 +1215,348 @@
     <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="6" customFormat="1">
       <c r="A1" s="6" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B18" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>14</v>
       </c>
       <c r="B20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1567,7 +1567,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="65.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.7109375" customWidth="1"/>
@@ -1581,9 +1581,9 @@
     <col min="11" max="11" width="74.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="18.75">
       <c r="A1" s="47" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="49"/>
@@ -1591,29 +1591,29 @@
       <c r="E1" s="49"/>
       <c r="F1" s="49"/>
     </row>
-    <row r="2" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="26.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="17" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="39"/>
@@ -1621,9 +1621,9 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="18" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B4" s="28">
         <v>375000</v>
@@ -1641,12 +1641,12 @@
         <v>ISIC 68</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="18" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="B5" s="28">
         <v>363636.36363636365</v>
@@ -1664,12 +1664,12 @@
         <v>ISIC 68</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="18" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="B6" s="28">
         <v>900000</v>
@@ -1687,12 +1687,12 @@
         <v>ISIC 69T82</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="18" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="B7" s="28">
         <v>675000</v>
@@ -1710,12 +1710,12 @@
         <v>ISIC 69T82</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="18" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="B8" s="28">
         <v>2313636.3636363638</v>
@@ -1724,36 +1724,36 @@
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="17" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="39"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="19" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="39"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="20" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B11" s="30">
         <v>600000</v>
@@ -1771,12 +1771,12 @@
         <v>ISIC 239</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="20" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="B12" s="30">
         <v>4950000</v>
@@ -1794,12 +1794,12 @@
         <v>ISIC 25</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" thickBot="1">
       <c r="A13" s="20" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="B13" s="30">
         <v>3300000</v>
@@ -1817,12 +1817,12 @@
         <v>ISIC 27</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="13" customFormat="1">
       <c r="A14" s="18" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="B14" s="31">
         <v>8850000</v>
@@ -1831,24 +1831,24 @@
       <c r="D14" s="45"/>
       <c r="E14" s="45"/>
       <c r="F14" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="17" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="39"/>
       <c r="D15" s="46"/>
       <c r="E15" s="46"/>
       <c r="F15" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="12" customFormat="1" ht="15.75" thickBot="1">
       <c r="A16" s="20" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="B16" s="30">
         <v>1765400.1798561153</v>
@@ -1866,12 +1866,12 @@
         <v>ISIC 41T43</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" thickBot="1">
       <c r="A17" s="20" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="B17" s="30">
         <v>3276000</v>
@@ -1889,12 +1889,12 @@
         <v>ISIC 41T43</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" thickBot="1">
       <c r="A18" s="18" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B18" s="31">
         <v>5041400.179856115</v>
@@ -1903,12 +1903,12 @@
       <c r="D18" s="3"/>
       <c r="E18" s="8"/>
       <c r="F18" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" thickBot="1">
       <c r="A19" s="21" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="B19" s="33">
         <v>16205036.543492477</v>
@@ -1917,36 +1917,36 @@
       <c r="D19" s="3"/>
       <c r="E19" s="7"/>
       <c r="F19" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" thickBot="1">
       <c r="A20" s="17" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="39"/>
       <c r="D20" s="3"/>
       <c r="E20" s="7"/>
       <c r="F20" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" thickBot="1">
       <c r="A21" s="19" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="B21" s="34"/>
       <c r="C21" s="39"/>
       <c r="D21" s="3"/>
       <c r="E21" s="8"/>
       <c r="F21" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" thickBot="1">
       <c r="A22" s="18" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="B22" s="31">
         <v>1800000</v>
@@ -1964,12 +1964,12 @@
         <v>ISIC 27</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" thickBot="1">
       <c r="A23" s="22" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B23" s="35">
         <v>650000</v>
@@ -1987,12 +1987,12 @@
         <v>ISIC 27</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" thickBot="1">
       <c r="A24" s="22" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="B24" s="35">
         <v>20000</v>
@@ -2010,12 +2010,12 @@
         <v>ISIC 27</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" thickBot="1">
       <c r="A25" s="18" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B25" s="31">
         <v>4800000</v>
@@ -2033,12 +2033,12 @@
         <v>ISIC 27</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1">
       <c r="A26" s="22" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="B26" s="35">
         <v>0</v>
@@ -2056,12 +2056,12 @@
         <v>ISIC 27</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" thickBot="1">
       <c r="A27" s="18" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="B27" s="31">
         <v>7270000</v>
@@ -2070,12 +2070,12 @@
       <c r="D27" s="3"/>
       <c r="E27" s="8"/>
       <c r="F27" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" thickBot="1">
       <c r="A28" s="17" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="B28" s="32"/>
       <c r="C28" s="39">
@@ -2085,12 +2085,12 @@
       <c r="D28" s="3"/>
       <c r="E28" s="7"/>
       <c r="F28" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" thickBot="1">
       <c r="A29" s="18" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="B29" s="31">
         <v>2092500</v>
@@ -2108,12 +2108,12 @@
         <v>ISIC 41T43</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" thickBot="1">
       <c r="A30" s="22" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="B30" s="35">
         <v>744000</v>
@@ -2131,12 +2131,12 @@
         <v>ISIC 41T43</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" thickBot="1">
       <c r="A31" s="22" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="B31" s="35">
         <v>27900</v>
@@ -2154,12 +2154,12 @@
         <v>ISIC 41T43</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" thickBot="1">
       <c r="A32" s="20" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B32" s="30">
         <v>0</v>
@@ -2177,12 +2177,12 @@
         <v>ISIC 41T43</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1">
       <c r="A33" s="20" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="B33" s="30">
         <v>0</v>
@@ -2200,12 +2200,12 @@
         <v>ISIC 41T43</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" thickBot="1">
       <c r="A34" s="18" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="B34" s="31">
         <v>2864400</v>
@@ -2214,12 +2214,12 @@
       <c r="D34" s="3"/>
       <c r="E34" s="7"/>
       <c r="F34" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1">
       <c r="A35" s="19" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="B35" s="34">
         <v>10134400</v>
@@ -2228,38 +2228,38 @@
       <c r="D35" s="3"/>
       <c r="E35" s="7"/>
       <c r="F35" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" thickBot="1">
       <c r="A36" s="17" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="3"/>
       <c r="E36" s="8"/>
       <c r="F36" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" thickBot="1">
       <c r="A37" s="17" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B37" s="32"/>
       <c r="C37" s="39"/>
       <c r="D37" s="3"/>
       <c r="E37" s="7"/>
       <c r="F37" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" thickBot="1">
       <c r="A38" s="18" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="B38" s="31">
         <v>375000</v>
@@ -2277,12 +2277,12 @@
         <v>ISIC 69T82</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" thickBot="1">
       <c r="A39" s="18" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="B39" s="31">
         <v>750000</v>
@@ -2300,12 +2300,12 @@
         <v>ISIC 69T82</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" thickBot="1">
       <c r="A40" s="18" t="s">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="B40" s="31">
         <v>1125000</v>
@@ -2314,24 +2314,24 @@
       <c r="D40" s="3"/>
       <c r="E40" s="7"/>
       <c r="F40" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" thickBot="1">
       <c r="A41" s="19" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B41" s="34"/>
       <c r="C41" s="39"/>
       <c r="D41" s="3"/>
       <c r="E41" s="7"/>
       <c r="F41" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" thickBot="1">
       <c r="A42" s="18" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="B42" s="31">
         <v>222000</v>
@@ -2349,12 +2349,12 @@
         <v>ISIC 69T82</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" thickBot="1">
       <c r="A43" s="18" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="B43" s="31">
         <v>1110000</v>
@@ -2372,12 +2372,12 @@
         <v>ISIC 69T82</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" thickBot="1">
       <c r="A44" s="18" t="s">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="B44" s="31">
         <v>1332000</v>
@@ -2386,24 +2386,24 @@
       <c r="D44" s="3"/>
       <c r="E44" s="7"/>
       <c r="F44" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" thickBot="1">
       <c r="A45" s="19" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="B45" s="34"/>
       <c r="C45" s="39"/>
       <c r="D45" s="3"/>
       <c r="E45" s="8"/>
       <c r="F45" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" thickBot="1">
       <c r="A46" s="20" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B46" s="30">
         <v>0</v>
@@ -2421,12 +2421,12 @@
         <v>ISIC 69T82</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1">
       <c r="A47" s="20" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="B47" s="30">
         <v>0</v>
@@ -2444,12 +2444,12 @@
         <v>ISIC 69T82</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" thickBot="1">
       <c r="A48" s="20" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="B48" s="30">
         <v>0</v>
@@ -2467,12 +2467,12 @@
         <v>ISIC 69T82</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" thickBot="1">
       <c r="A49" s="23" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B49" s="30">
         <v>55500</v>
@@ -2490,12 +2490,12 @@
         <v>ISIC 64T66</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" thickBot="1">
       <c r="A50" s="20" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="B50" s="30">
         <v>55500</v>
@@ -2504,12 +2504,12 @@
       <c r="D50" s="3"/>
       <c r="E50" s="7"/>
       <c r="F50" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1">
       <c r="A51" s="24" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="B51" s="36">
         <v>2512500</v>
@@ -2518,12 +2518,12 @@
       <c r="D51" s="3"/>
       <c r="E51" s="8"/>
       <c r="F51" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" thickBot="1">
       <c r="A52" s="17" t="s">
-        <v>2</v>
+        <v>143</v>
       </c>
       <c r="B52" s="37">
         <v>28851936.543492477</v>
@@ -2532,12 +2532,12 @@
       <c r="D52" s="3"/>
       <c r="E52" s="7"/>
       <c r="F52" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1">
       <c r="A53" s="25" t="s">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="B53" s="38">
         <v>1007500</v>
@@ -2546,21 +2546,21 @@
       <c r="D53" s="3"/>
       <c r="E53" s="7"/>
       <c r="F53" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="19" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B54" s="19">
         <v>29859436.543492477</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="C55" s="40"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="C56" s="40"/>
     </row>
   </sheetData>
@@ -2578,7 +2578,7 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AQ10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="26" width="10.42578125" customWidth="1"/>
@@ -2587,140 +2587,140 @@
     <col min="29" max="43" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43">
       <c r="A1" s="44" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="B1" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="D1" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="43" t="s">
+      <c r="P1" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="43" t="s">
+      <c r="Q1" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="43" t="s">
+      <c r="R1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="M1" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="N1" s="43" t="s">
+      <c r="S1" s="43" t="s">
         <v>43</v>
-      </c>
-      <c r="O1" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="P1" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q1" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="R1" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="S1" s="43" t="s">
-        <v>44</v>
       </c>
       <c r="T1" s="43" t="s">
         <v>45</v>
       </c>
       <c r="U1" s="43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V1" s="43" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="W1" s="43" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="X1" s="43" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Y1" s="43" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="43" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="AA1" s="43" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="AB1" s="43" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="AC1" s="43" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="AD1" s="43" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="AE1" s="43" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AF1" s="43" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="AG1" s="43" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="AH1" s="43" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="AI1" s="43" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AJ1" s="43" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="AK1" s="43" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="AL1" s="43" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="AM1" s="43" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="AN1" s="43" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="AO1" s="43" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="AP1" s="43" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="AQ1" s="43" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="B2" s="10">
         <f>SUMIF('Cost Breakdowns'!$E$3:$E$49,SoTaDCCbIC!B$1,'Cost Breakdowns'!$C$3:$C$49)</f>
@@ -2891,11 +2891,182 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43">
       <c r="F10" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE796BBD-9A89-4A2E-B52B-FE97DB36540C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C56B1E6B-1E01-4305-A8E2-7575B87CBC99}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56F9D5F9-C56A-4DAC-B735-F03C941FC36E}"/>
 </file>